--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/16_expert_lenses.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/16_expert_lenses.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R5709cccfe34f4021"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R7097274f35b443c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R3c3911ed39454f5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R66ed72cc15104ca8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rf15060ceb8ec4d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Ra7916d449d834ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rd90b1c09b7994047"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R20398a5de3554797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R965820d81d4a4c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R71cb03c6a95c49a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R7a93034af7d94096"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R86decfa33ab84cda"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -618,7 +618,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R026d0871bef743c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd47e6b68a8f64388"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -749,7 +749,7 @@
         <x:v>Chief Strategy Officer</x:v>
       </x:c>
       <x:c r="J6" s="78" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Validate selected record (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for expert lenses.</x:v>
       </x:c>
       <x:c r="K6" s="41" t="str">
         <x:v>High</x:v>
@@ -784,7 +784,7 @@
         <x:v>Retail Banking COO</x:v>
       </x:c>
       <x:c r="J7" s="79" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Confirm selected record (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this expert lenses record is used downstream.</x:v>
       </x:c>
       <x:c r="K7" s="45" t="str">
         <x:v>High</x:v>
@@ -819,7 +819,7 @@
         <x:v>Commercial Banking COO</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Attach client evidence for selected record (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K8" t="str">
         <x:v>High</x:v>
@@ -854,7 +854,7 @@
         <x:v>Head of Cards</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Reconcile selected record (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K9" t="str">
         <x:v>High</x:v>
@@ -889,7 +889,7 @@
         <x:v>Payments Leader</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K10" t="str">
         <x:v>High</x:v>
@@ -924,7 +924,7 @@
         <x:v>Head of Consumer Lending</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Validate selected record (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for expert lenses.</x:v>
       </x:c>
       <x:c r="K11" t="str">
         <x:v>High</x:v>
@@ -959,7 +959,7 @@
         <x:v>Head of Wealth</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Confirm selected record (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this expert lenses record is used downstream.</x:v>
       </x:c>
       <x:c r="K12" t="str">
         <x:v>High</x:v>
@@ -994,7 +994,7 @@
         <x:v>CRO</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Validate selected record (record 8) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="K13" t="str">
         <x:v>High</x:v>
@@ -1029,7 +1029,7 @@
         <x:v>Chief Compliance Officer</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Reconcile selected record (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K14" t="str">
         <x:v>High</x:v>
@@ -1064,7 +1064,7 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K15" t="str">
         <x:v>High</x:v>
@@ -1099,7 +1099,7 @@
         <x:v>Digital Banking Product Owner</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Validate selected record (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for expert lenses.</x:v>
       </x:c>
       <x:c r="K16" t="str">
         <x:v>High</x:v>
@@ -1134,7 +1134,7 @@
         <x:v>CIO</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Confirm selected record (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this expert lenses record is used downstream.</x:v>
       </x:c>
       <x:c r="K17" t="str">
         <x:v>High</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Attach client evidence for selected record (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K18" t="str">
         <x:v>High</x:v>
@@ -1204,7 +1204,7 @@
         <x:v>Retail Analytics Lead</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Reconcile selected record (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K19" t="str">
         <x:v>High</x:v>
@@ -1239,7 +1239,7 @@
         <x:v>Cards Analytics Lead</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K20" t="str">
         <x:v>High</x:v>
@@ -1274,7 +1274,7 @@
         <x:v>Payments Analytics Lead</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Validate selected record (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for expert lenses.</x:v>
       </x:c>
       <x:c r="K21" t="str">
         <x:v>High</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>Fraud Analytics Lead</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Validate selected record (record 17) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="K22" t="str">
         <x:v>High</x:v>
@@ -1344,7 +1344,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Attach client evidence for selected record (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="K23" t="str">
         <x:v>High</x:v>
@@ -1379,7 +1379,7 @@
         <x:v>CIO / CFO</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Reconcile selected record (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="K24" t="str">
         <x:v>High</x:v>
@@ -1414,7 +1414,7 @@
         <x:v>Chief Procurement Officer</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for selected record (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="K25" t="str">
         <x:v>High</x:v>
@@ -1449,7 +1449,7 @@
         <x:v>CTO</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Validate selected record (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for expert lenses.</x:v>
       </x:c>
       <x:c r="K26" t="str">
         <x:v>High</x:v>
@@ -1484,7 +1484,7 @@
         <x:v>VP IT Operations</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>Need client-specific decision thresholds and board/CXO priorities.</x:v>
+        <x:v>Confirm selected record (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this expert lenses record is used downstream.</x:v>
       </x:c>
       <x:c r="K27" t="str">
         <x:v>High</x:v>
@@ -1505,7 +1505,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd28775153c34143"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86806299370a46b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1580,7 +1580,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08ed095b593a4eb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fffc00242ac4fd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1724,7 +1724,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bdc2faefe4e48da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45e68c806a124124"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1786,7 +1786,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf13a796e67f4834"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8ff0ba303547a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1896,7 +1896,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R059a8176979f4f53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3882f152ca134538"/>
   </x:tableParts>
 </x:worksheet>
 </file>